--- a/docs/TestSummaryReport.xlsx
+++ b/docs/TestSummaryReport.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Summary Report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Summary Report'!$A$1:$B$35</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,44 +28,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0027AE60"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001A3A5C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001A5276"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -76,37 +60,36 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00B7B7B7"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00B7B7B7"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00B7B7B7"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00B7B7B7"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -472,14 +455,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Field</t>
@@ -491,7 +474,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Project Name</t>
@@ -503,7 +486,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1">
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Application</t>
@@ -515,7 +498,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Test Cycle</t>
@@ -523,11 +506,11 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Capstone — June 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
+          <t>Capstone - June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Prepared By</t>
@@ -539,7 +522,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Report Date</t>
@@ -547,71 +530,63 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>June 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
+          <t>June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="22" customHeight="1">
+    <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>TEST EXECUTION SUMMARY</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
+      <c r="B8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Total Test Cases</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
+      <c r="B9" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
+      <c r="B10" s="3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
+      <c r="B11" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
+      <c r="B12" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Pass %</t>
@@ -619,243 +594,216 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
+          <t>73%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="3" t="inlineStr"/>
     </row>
-    <row r="15" ht="22" customHeight="1">
+    <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>TEST TYPE BREAKDOWN</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
+      <c r="B15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>UI Tests</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
+      <c r="B16" s="3" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>API Tests</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
+      <c r="B17" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Hybrid E2E Tests</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Performance Tests</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B18" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>DEFECT SUMMARY</t>
+        </is>
+      </c>
       <c r="B20" s="3" t="inlineStr"/>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>DEFECT SUMMARY</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Total Defects</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Total Defects</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
+          <t>High Severity</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>High Severity</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
+          <t>Medium Severity</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Medium Severity</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>1 - transferHybrid intermittent issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
           <t>Low Severity</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B24" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>AUTOMATION SUMMARY</t>
+        </is>
+      </c>
       <c r="B26" s="3" t="inlineStr"/>
     </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>AUTOMATION SUMMARY</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Framework</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Playwright + TypeScript</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Framework</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Playwright + TypeScript</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
+          <t>Page Object Model (POM) + API Fixtures</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Browsers</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Page Object Model (POM) + API Fixtures</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
+          <t>Chromium + Firefox + WebKit (Parallel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Browsers</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Chrome + Firefox (Parallel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
+          <t>Retries on CI</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Retries on CI</t>
+          <t>Tags Used</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
+          <t>@smoke, @regression, @api, @e2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Tags Used</t>
+          <t>CI/CD</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>@smoke, @regression, @api, @e2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
+          <t>GitHub Actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>CI/CD</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>GitHub Actions</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Reports</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Playwright HTML Report, Allure Report, Failure Analysis HTML</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
+          <t>Playwright HTML Report, Allure Report, AI Failure Analysis Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>OVERALL STATUS</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>PASS WITH MINOR DEFECTS</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>